--- a/vault/06 Assets/Art Assets.xlsx
+++ b/vault/06 Assets/Art Assets.xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>mixed media neutral</t>
+          <t>gold waistup</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>stand-in (neutral)</t>
+          <t>gold waistup</t>
         </is>
       </c>
     </row>
